--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,85 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/10 Octubre/Liquidacióncvs -oct/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_58B5E9E9D464F80E62355476585DCE3A8744F61A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC13706F-3B9F-4037-9897-92B4E0105F26}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Producto</t>
-  </si>
-  <si>
-    <t>Meta_Producto</t>
-  </si>
-  <si>
-    <t>Ejecutado</t>
-  </si>
-  <si>
-    <t>% Cumplimiento</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Rol</t>
-  </si>
-  <si>
-    <t>CVS</t>
-  </si>
-  <si>
-    <t>Mes</t>
-  </si>
-  <si>
-    <t>Tipo Pago Comisión</t>
-  </si>
-  <si>
-    <t>Observación</t>
-  </si>
-  <si>
-    <t>ACC</t>
-  </si>
-  <si>
-    <t>% Cumplimiento Puntos</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -94,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -418,46 +420,1278 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Meta_Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ejecutado</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>% Cumplimiento</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Rol</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo Pago Comisión</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>% Cumplimiento Puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>112</v>
+      </c>
+      <c r="C5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>142%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>335</v>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1562647</v>
+      </c>
+      <c r="C7" t="n">
+        <v>530000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Vacaciones del 28 de septiembre al 15 de octubre</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>32</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>72</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>215</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1004706</v>
+      </c>
+      <c r="C13" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>28</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>70</v>
+      </c>
+      <c r="C16" t="n">
+        <v>58</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>158</v>
+      </c>
+      <c r="C17" t="n">
+        <v>87</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>100</v>
+      </c>
+      <c r="L17" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>475</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2216324</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1248400</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>44</v>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
+      <c r="L20" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>100</v>
+      </c>
+      <c r="L21" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>70</v>
+      </c>
+      <c r="C22" t="n">
+        <v>33</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>100</v>
+      </c>
+      <c r="L22" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>158</v>
+      </c>
+      <c r="C23" t="n">
+        <v>66</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L23" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>475</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2216324</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1874500</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>100</v>
+      </c>
+      <c r="L25" t="n">
+        <v>49.9</v>
       </c>
     </row>
   </sheetData>
